--- a/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
+++ b/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
@@ -1,20 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data-portfolio\excel-analysis\analysis-cafe\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374F0FA-2B85-4663-8A44-304FCC86C6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="데이터" sheetId="1" r:id="rId1"/>
+    <sheet name="분석" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">데이터!$D$1:$D$91</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -37,25 +80,7 @@
     <t>매출</t>
   </si>
   <si>
-    <t>일</t>
-  </si>
-  <si>
-    <t>목</t>
-  </si>
-  <si>
-    <t>화</t>
-  </si>
-  <si>
-    <t>토</t>
-  </si>
-  <si>
     <t>월</t>
-  </si>
-  <si>
-    <t>수</t>
-  </si>
-  <si>
-    <t>금</t>
   </si>
   <si>
     <t>오후</t>
@@ -81,15 +106,45 @@
   <si>
     <t>아인슈페너</t>
   </si>
+  <si>
+    <t>요일(숫자형)</t>
+  </si>
+  <si>
+    <t>주말 여부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">매출 합계 </t>
+  </si>
+  <si>
+    <t>매출 평균</t>
+  </si>
+  <si>
+    <t>최대 매출</t>
+  </si>
+  <si>
+    <t>최소 매출</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 인기 메뉴</t>
+  </si>
+  <si>
+    <t>비 인기 메뉴</t>
+  </si>
+  <si>
+    <t>메뉴 종류</t>
+  </si>
+  <si>
+    <t>판매량</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,25 +196,202 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -197,7 +429,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -231,6 +463,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,9 +498,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,12 +674,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -466,19 +708,32 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>45839</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B2" t="str">
+        <f>TEXT(A2, "dddd")</f>
+        <v>martes</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -486,22 +741,39 @@
       <c r="F2">
         <v>3000</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="7">
         <v>15000</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
+      <c r="H2">
+        <f>MONTH(A2)</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="2">
+        <f>WEEKDAY(A2)</f>
+        <v>3</v>
+      </c>
+      <c r="J2" s="5" t="str">
+        <f>IF((I2=1)+(I2=7),"finde","semana")</f>
+        <v>semana</v>
+      </c>
+      <c r="K2" s="6">
+        <f>SUM(G2:G91)</f>
+        <v>1038700</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>45840</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
+      <c r="B3" t="str">
+        <f t="shared" ref="B3:B66" si="0">TEXT(A3, "dddd")</f>
+        <v>miércoles</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -509,22 +781,35 @@
       <c r="F3">
         <v>3500</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="7">
         <v>17500</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
+      <c r="H3">
+        <f t="shared" ref="H3:H66" si="1">MONTH(A3)</f>
+        <v>7</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I66" si="2">WEEKDAY(A3)</f>
+        <v>4</v>
+      </c>
+      <c r="J3" s="5" t="str">
+        <f t="shared" ref="J3:J66" si="3">IF((I3=1)+(I3=7),"finde","semana")</f>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>45841</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -532,22 +817,38 @@
       <c r="F4">
         <v>3800</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J4" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>45842</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -555,22 +856,39 @@
       <c r="F5">
         <v>3500</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J5" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K5" s="6">
+        <f>AVERAGE(G2:G91)</f>
+        <v>11541.111111111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>45843</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -578,22 +896,35 @@
       <c r="F6">
         <v>3000</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="7">
         <v>15000</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J6" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>45844</v>
       </c>
-      <c r="B7" t="s">
-        <v>10</v>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -601,22 +932,41 @@
       <c r="F7">
         <v>3500</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="7">
         <v>17500</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>45845</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -624,22 +974,43 @@
       <c r="F8">
         <v>3800</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J8" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K8" s="6">
+        <f>MAX(G2:G91)</f>
+        <v>22500</v>
+      </c>
+      <c r="L8" s="6">
+        <f>MIN(G2:G91)</f>
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>45846</v>
       </c>
-      <c r="B9" t="s">
-        <v>9</v>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -647,22 +1018,35 @@
       <c r="F9">
         <v>3500</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>3500</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2">
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J9" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>45847</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
         <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -670,22 +1054,41 @@
       <c r="F10">
         <v>3500</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2">
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J10" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>45848</v>
       </c>
-      <c r="B11" t="s">
-        <v>7</v>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -693,22 +1096,43 @@
       <c r="F11">
         <v>3000</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J11" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K11" t="str" cm="1">
+        <f t="array" ref="K11:K15">_xlfn.UNIQUE(D2:D91)</f>
+        <v>아메리카노</v>
+      </c>
+      <c r="L11">
+        <f>COUNTIF(D2:D91, K11)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <v>45849</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -716,22 +1140,42 @@
       <c r="F12">
         <v>3800</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="7">
         <v>7600</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2">
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J12" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K12" t="str">
+        <v>라떼</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12:L15" si="4">COUNTIF(D3:D92, K12)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>45850</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
+      </c>
+      <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -739,22 +1183,42 @@
       <c r="F13">
         <v>3000</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J13" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+      <c r="K13" t="str">
+        <v>바닐라라떼</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <v>45851</v>
       </c>
-      <c r="B14" t="s">
-        <v>7</v>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -762,22 +1226,42 @@
       <c r="F14">
         <v>3800</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2">
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+      <c r="K14" t="str">
+        <v>카푸치노</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>45852</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -785,22 +1269,42 @@
       <c r="F15">
         <v>3800</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="7">
         <v>15200</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2">
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J15" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K15" t="str">
+        <v>아인슈페너</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>45853</v>
       </c>
-      <c r="B16" t="s">
-        <v>13</v>
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
         <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -808,22 +1312,35 @@
       <c r="F16">
         <v>3300</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="7">
         <v>3300</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2">
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J16" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>45854</v>
       </c>
-      <c r="B17" t="s">
-        <v>9</v>
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -831,22 +1348,41 @@
       <c r="F17">
         <v>3300</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="7">
         <v>3300</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2">
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J17" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <v>45855</v>
       </c>
-      <c r="B18" t="s">
-        <v>13</v>
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -854,22 +1390,43 @@
       <c r="F18">
         <v>3500</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J18" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K18" t="str" cm="1">
+        <f t="array" ref="K18">_xlfn.XLOOKUP(MAX(L11:L15), L11:L15,_xlfn.ANCHORARRAY(K11))</f>
+        <v>바닐라라떼</v>
+      </c>
+      <c r="L18" t="str" cm="1">
+        <f t="array" ref="L18:L19">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(K11),L11:L15 = MIN(L11:L15))</f>
+        <v>아메리카노</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>45856</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -877,22 +1434,38 @@
       <c r="F19">
         <v>3500</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="7">
         <v>7000</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2">
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J19" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="L19" t="str">
+        <v>카푸치노</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
         <v>45857</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E20">
         <v>4</v>
@@ -900,22 +1473,35 @@
       <c r="F20">
         <v>3500</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2">
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J20" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <v>45858</v>
       </c>
-      <c r="B21" t="s">
-        <v>11</v>
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -923,22 +1509,35 @@
       <c r="F21">
         <v>3500</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="7">
         <v>3500</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2">
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <v>45859</v>
       </c>
-      <c r="B22" t="s">
-        <v>7</v>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -946,22 +1545,35 @@
       <c r="F22">
         <v>4500</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="7">
         <v>4500</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2">
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J22" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>45860</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
         <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>17</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -969,22 +1581,35 @@
       <c r="F23">
         <v>3000</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2">
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <v>45861</v>
       </c>
-      <c r="B24" t="s">
-        <v>7</v>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -992,22 +1617,35 @@
       <c r="F24">
         <v>3500</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2">
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J24" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <v>45862</v>
       </c>
-      <c r="B25" t="s">
-        <v>7</v>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>2</v>
@@ -1015,22 +1653,35 @@
       <c r="F25">
         <v>3300</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="7">
         <v>6600</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="2">
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J25" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
         <v>45863</v>
       </c>
-      <c r="B26" t="s">
-        <v>8</v>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -1038,22 +1689,35 @@
       <c r="F26">
         <v>3800</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="7">
         <v>15200</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2">
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J26" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
         <v>45864</v>
       </c>
-      <c r="B27" t="s">
-        <v>13</v>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
         <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1061,22 +1725,35 @@
       <c r="F27">
         <v>4500</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="2">
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J27" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
         <v>45865</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1084,22 +1761,35 @@
       <c r="F28">
         <v>4500</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="7">
         <v>22500</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="2">
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J28" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
         <v>45866</v>
       </c>
-      <c r="B29" t="s">
-        <v>12</v>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1107,22 +1797,35 @@
       <c r="F29">
         <v>3000</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="2">
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J29" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
         <v>45867</v>
       </c>
-      <c r="B30" t="s">
-        <v>11</v>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -1130,22 +1833,35 @@
       <c r="F30">
         <v>3500</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="2">
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J30" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
         <v>45868</v>
       </c>
-      <c r="B31" t="s">
-        <v>10</v>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -1153,22 +1869,35 @@
       <c r="F31">
         <v>3000</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2">
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I31" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J31" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
         <v>45869</v>
       </c>
-      <c r="B32" t="s">
-        <v>9</v>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>5</v>
@@ -1176,22 +1905,35 @@
       <c r="F32">
         <v>3300</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="7">
         <v>16500</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2">
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J32" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
         <v>45870</v>
       </c>
-      <c r="B33" t="s">
-        <v>12</v>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s">
         <v>15</v>
-      </c>
-      <c r="D33" t="s">
-        <v>21</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -1199,22 +1941,35 @@
       <c r="F33">
         <v>4500</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2">
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I33" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J33" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>45871</v>
       </c>
-      <c r="B34" t="s">
-        <v>11</v>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E34">
         <v>4</v>
@@ -1222,22 +1977,35 @@
       <c r="F34">
         <v>3500</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="2">
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I34" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
         <v>45872</v>
       </c>
-      <c r="B35" t="s">
-        <v>8</v>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1245,22 +2013,35 @@
       <c r="F35">
         <v>4500</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2">
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I35" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J35" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
         <v>45873</v>
       </c>
-      <c r="B36" t="s">
-        <v>8</v>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -1268,22 +2049,35 @@
       <c r="F36">
         <v>3800</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="2">
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I36" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J36" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
         <v>45874</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
         <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" t="s">
-        <v>19</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -1291,22 +2085,35 @@
       <c r="F37">
         <v>3800</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="2">
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I37" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J37" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>45875</v>
       </c>
-      <c r="B38" t="s">
-        <v>8</v>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
         <v>15</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -1314,22 +2121,35 @@
       <c r="F38">
         <v>4500</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="2">
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I38" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J38" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
         <v>45876</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
         <v>12</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -1337,22 +2157,35 @@
       <c r="F39">
         <v>3500</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="7">
         <v>17500</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="2">
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I39" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J39" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
         <v>45877</v>
       </c>
-      <c r="B40" t="s">
-        <v>8</v>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -1360,22 +2193,35 @@
       <c r="F40">
         <v>4500</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="2">
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I40" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J40" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
         <v>45878</v>
       </c>
-      <c r="B41" t="s">
-        <v>11</v>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
         <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>20</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1383,22 +2229,35 @@
       <c r="F41">
         <v>3300</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="7">
         <v>3300</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="2">
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I41" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
         <v>45879</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
+      </c>
+      <c r="C42" t="s">
         <v>10</v>
       </c>
-      <c r="C42" t="s">
-        <v>16</v>
-      </c>
       <c r="D42" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E42">
         <v>5</v>
@@ -1406,22 +2265,35 @@
       <c r="F42">
         <v>3300</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="7">
         <v>16500</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="2">
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I42" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J42" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>45880</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
         <v>13</v>
-      </c>
-      <c r="C43" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" t="s">
-        <v>19</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -1429,22 +2301,35 @@
       <c r="F43">
         <v>3800</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="2">
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I43" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J43" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>45881</v>
       </c>
-      <c r="B44" t="s">
-        <v>9</v>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E44">
         <v>5</v>
@@ -1452,22 +2337,35 @@
       <c r="F44">
         <v>3000</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="7">
         <v>15000</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="2">
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I44" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J44" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
         <v>45882</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
         <v>13</v>
-      </c>
-      <c r="C45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" t="s">
-        <v>19</v>
       </c>
       <c r="E45">
         <v>5</v>
@@ -1475,22 +2373,35 @@
       <c r="F45">
         <v>3800</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="2">
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I45" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J45" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
         <v>45883</v>
       </c>
-      <c r="B46" t="s">
-        <v>12</v>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -1498,22 +2409,35 @@
       <c r="F46">
         <v>3000</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="2">
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I46" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J46" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
         <v>45884</v>
       </c>
-      <c r="B47" t="s">
-        <v>8</v>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>4</v>
@@ -1521,22 +2445,35 @@
       <c r="F47">
         <v>4500</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="7">
         <v>18000</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="2">
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I47" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J47" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
         <v>45885</v>
       </c>
-      <c r="B48" t="s">
-        <v>9</v>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -1544,22 +2481,35 @@
       <c r="F48">
         <v>3500</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="2">
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I48" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J48" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
         <v>45886</v>
       </c>
-      <c r="B49" t="s">
-        <v>8</v>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>2</v>
@@ -1567,22 +2517,35 @@
       <c r="F49">
         <v>3500</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="7">
         <v>7000</v>
       </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="2">
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I49" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
         <v>45887</v>
       </c>
-      <c r="B50" t="s">
-        <v>10</v>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
         <v>15</v>
-      </c>
-      <c r="D50" t="s">
-        <v>21</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -1590,22 +2553,35 @@
       <c r="F50">
         <v>4500</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="2">
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I50" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J50" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
         <v>45888</v>
       </c>
-      <c r="B51" t="s">
-        <v>8</v>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -1613,22 +2589,35 @@
       <c r="F51">
         <v>3000</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="2">
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I51" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J51" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
         <v>45889</v>
       </c>
-      <c r="B52" t="s">
-        <v>13</v>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -1636,22 +2625,35 @@
       <c r="F52">
         <v>3300</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="7">
         <v>9900</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="2">
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I52" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J52" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
         <v>45890</v>
       </c>
-      <c r="B53" t="s">
-        <v>8</v>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -1659,22 +2661,35 @@
       <c r="F53">
         <v>3500</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="2">
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I53" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J53" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
         <v>45891</v>
       </c>
-      <c r="B54" t="s">
-        <v>7</v>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -1682,22 +2697,35 @@
       <c r="F54">
         <v>3500</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="2">
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I54" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J54" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
         <v>45892</v>
       </c>
-      <c r="B55" t="s">
-        <v>8</v>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -1705,22 +2733,35 @@
       <c r="F55">
         <v>3500</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="2">
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I55" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J55" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
         <v>45893</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
         <v>13</v>
-      </c>
-      <c r="C56" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -1728,22 +2769,35 @@
       <c r="F56">
         <v>3800</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="2">
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I56" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J56" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
         <v>45894</v>
       </c>
-      <c r="B57" t="s">
-        <v>9</v>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -1751,22 +2805,35 @@
       <c r="F57">
         <v>4500</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="2">
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I57" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J57" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
         <v>45895</v>
       </c>
-      <c r="B58" t="s">
-        <v>12</v>
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>5</v>
@@ -1774,22 +2841,35 @@
       <c r="F58">
         <v>4500</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="7">
         <v>22500</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="2">
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I58" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J58" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
         <v>45896</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
         <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" t="s">
-        <v>19</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -1797,22 +2877,35 @@
       <c r="F59">
         <v>3800</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="7">
         <v>7600</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="2">
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I59" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J59" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
         <v>45897</v>
       </c>
-      <c r="B60" t="s">
-        <v>10</v>
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>jueves</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1820,22 +2913,35 @@
       <c r="F60">
         <v>3800</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="7">
         <v>3800</v>
       </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="2">
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J60" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
         <v>45898</v>
       </c>
-      <c r="B61" t="s">
-        <v>11</v>
+      <c r="B61" t="str">
+        <f t="shared" si="0"/>
+        <v>viernes</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -1843,22 +2949,35 @@
       <c r="F61">
         <v>3300</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="7">
         <v>3300</v>
       </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="2">
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I61" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J61" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
         <v>45899</v>
       </c>
-      <c r="B62" t="s">
-        <v>8</v>
+      <c r="B62" t="str">
+        <f t="shared" si="0"/>
+        <v>sábado</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -1866,22 +2985,35 @@
       <c r="F62">
         <v>3000</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="2">
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I62" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J62" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
         <v>45900</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" t="str">
+        <f t="shared" si="0"/>
+        <v>domingo</v>
+      </c>
+      <c r="C63" t="s">
         <v>10</v>
       </c>
-      <c r="C63" t="s">
-        <v>16</v>
-      </c>
       <c r="D63" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -1889,22 +3021,35 @@
       <c r="F63">
         <v>3300</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="7">
         <v>6600</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="2">
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I63" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J63" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
         <v>45901</v>
       </c>
-      <c r="B64" t="s">
-        <v>10</v>
+      <c r="B64" t="str">
+        <f t="shared" si="0"/>
+        <v>lunes</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -1912,22 +3057,35 @@
       <c r="F64">
         <v>3800</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="2">
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I64" s="2">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J64" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
         <v>45902</v>
       </c>
-      <c r="B65" t="s">
-        <v>9</v>
+      <c r="B65" t="str">
+        <f t="shared" si="0"/>
+        <v>martes</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -1935,22 +3093,35 @@
       <c r="F65">
         <v>4500</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="7">
         <v>18000</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="2">
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I65" s="2">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J65" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
         <v>45903</v>
       </c>
-      <c r="B66" t="s">
-        <v>8</v>
+      <c r="B66" t="str">
+        <f t="shared" si="0"/>
+        <v>miércoles</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E66">
         <v>5</v>
@@ -1958,22 +3129,35 @@
       <c r="F66">
         <v>4500</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="7">
         <v>22500</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="2">
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I66" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J66" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
         <v>45904</v>
       </c>
-      <c r="B67" t="s">
-        <v>12</v>
+      <c r="B67" t="str">
+        <f t="shared" ref="B67:B91" si="5">TEXT(A67, "dddd")</f>
+        <v>jueves</v>
       </c>
       <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
         <v>15</v>
-      </c>
-      <c r="D67" t="s">
-        <v>21</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -1981,22 +3165,35 @@
       <c r="F67">
         <v>4500</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="7">
         <v>18000</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="2">
+      <c r="H67">
+        <f t="shared" ref="H67:H91" si="6">MONTH(A67)</f>
+        <v>9</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" ref="I67:I91" si="7">WEEKDAY(A67)</f>
+        <v>5</v>
+      </c>
+      <c r="J67" s="5" t="str">
+        <f t="shared" ref="J67:J91" si="8">IF((I67=1)+(I67=7),"finde","semana")</f>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
         <v>45905</v>
       </c>
-      <c r="B68" t="s">
-        <v>8</v>
+      <c r="B68" t="str">
+        <f t="shared" si="5"/>
+        <v>viernes</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -2004,22 +3201,35 @@
       <c r="F68">
         <v>3800</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="7">
         <v>7600</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="2">
+      <c r="H68">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="J68" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
         <v>45906</v>
       </c>
-      <c r="B69" t="s">
-        <v>12</v>
+      <c r="B69" t="str">
+        <f t="shared" si="5"/>
+        <v>sábado</v>
       </c>
       <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
         <v>15</v>
-      </c>
-      <c r="D69" t="s">
-        <v>21</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -2027,22 +3237,35 @@
       <c r="F69">
         <v>4500</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="7">
         <v>18000</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2">
+      <c r="H69">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J69" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
         <v>45907</v>
       </c>
-      <c r="B70" t="s">
-        <v>8</v>
+      <c r="B70" t="str">
+        <f t="shared" si="5"/>
+        <v>domingo</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -2050,22 +3273,35 @@
       <c r="F70">
         <v>3000</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="2">
+      <c r="H70">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="J70" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
         <v>45908</v>
       </c>
-      <c r="B71" t="s">
-        <v>10</v>
+      <c r="B71" t="str">
+        <f t="shared" si="5"/>
+        <v>lunes</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -2073,22 +3309,35 @@
       <c r="F71">
         <v>3800</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="2">
+      <c r="H71">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="J71" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
         <v>45909</v>
       </c>
-      <c r="B72" t="s">
-        <v>11</v>
+      <c r="B72" t="str">
+        <f t="shared" si="5"/>
+        <v>martes</v>
       </c>
       <c r="C72" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" t="s">
         <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>20</v>
       </c>
       <c r="E72">
         <v>4</v>
@@ -2096,22 +3345,35 @@
       <c r="F72">
         <v>3300</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="7">
         <v>13200</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="2">
+      <c r="H72">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="J72" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
         <v>45910</v>
       </c>
-      <c r="B73" t="s">
-        <v>13</v>
+      <c r="B73" t="str">
+        <f t="shared" si="5"/>
+        <v>miércoles</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E73">
         <v>4</v>
@@ -2119,22 +3381,35 @@
       <c r="F73">
         <v>3500</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="7">
         <v>14000</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="2">
+      <c r="H73">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="J73" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
         <v>45911</v>
       </c>
-      <c r="B74" t="s">
-        <v>7</v>
+      <c r="B74" t="str">
+        <f t="shared" si="5"/>
+        <v>jueves</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -2142,22 +3417,35 @@
       <c r="F74">
         <v>4500</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="7">
         <v>9000</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="2">
+      <c r="H74">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I74" s="2">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J74" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
         <v>45912</v>
       </c>
-      <c r="B75" t="s">
-        <v>11</v>
+      <c r="B75" t="str">
+        <f t="shared" si="5"/>
+        <v>viernes</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E75">
         <v>5</v>
@@ -2165,22 +3453,35 @@
       <c r="F75">
         <v>3800</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="2">
+      <c r="H75">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I75" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="J75" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
         <v>45913</v>
       </c>
-      <c r="B76" t="s">
-        <v>12</v>
+      <c r="B76" t="str">
+        <f t="shared" si="5"/>
+        <v>sábado</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -2188,22 +3489,35 @@
       <c r="F76">
         <v>4500</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="7">
         <v>4500</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="2">
+      <c r="H76">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I76" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J76" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
         <v>45914</v>
       </c>
-      <c r="B77" t="s">
-        <v>12</v>
+      <c r="B77" t="str">
+        <f t="shared" si="5"/>
+        <v>domingo</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -2211,22 +3525,35 @@
       <c r="F77">
         <v>4500</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="2">
+      <c r="H77">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I77" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="J77" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
         <v>45915</v>
       </c>
-      <c r="B78" t="s">
-        <v>10</v>
+      <c r="B78" t="str">
+        <f t="shared" si="5"/>
+        <v>lunes</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -2234,22 +3561,35 @@
       <c r="F78">
         <v>3800</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="7">
         <v>3800</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="2">
+      <c r="H78">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I78" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="J78" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
         <v>45916</v>
       </c>
-      <c r="B79" t="s">
-        <v>7</v>
+      <c r="B79" t="str">
+        <f t="shared" si="5"/>
+        <v>martes</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -2257,22 +3597,35 @@
       <c r="F79">
         <v>3300</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="7">
         <v>6600</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="2">
+      <c r="H79">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I79" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="J79" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
         <v>45917</v>
       </c>
-      <c r="B80" t="s">
-        <v>7</v>
+      <c r="B80" t="str">
+        <f t="shared" si="5"/>
+        <v>miércoles</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E80">
         <v>2</v>
@@ -2280,22 +3633,35 @@
       <c r="F80">
         <v>3000</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="7">
         <v>6000</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="2">
+      <c r="H80">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I80" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="J80" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
         <v>45918</v>
       </c>
-      <c r="B81" t="s">
-        <v>13</v>
+      <c r="B81" t="str">
+        <f t="shared" si="5"/>
+        <v>jueves</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E81">
         <v>4</v>
@@ -2303,22 +3669,35 @@
       <c r="F81">
         <v>3000</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="7">
         <v>12000</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="2">
+      <c r="H81">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I81" s="2">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J81" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
         <v>45919</v>
       </c>
-      <c r="B82" t="s">
-        <v>10</v>
+      <c r="B82" t="str">
+        <f t="shared" si="5"/>
+        <v>viernes</v>
       </c>
       <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
         <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>20</v>
       </c>
       <c r="E82">
         <v>5</v>
@@ -2326,22 +3705,35 @@
       <c r="F82">
         <v>3300</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="7">
         <v>16500</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="2">
+      <c r="H82">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I82" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="J82" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
         <v>45920</v>
       </c>
-      <c r="B83" t="s">
-        <v>8</v>
+      <c r="B83" t="str">
+        <f t="shared" si="5"/>
+        <v>sábado</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -2349,22 +3741,35 @@
       <c r="F83">
         <v>3500</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="7">
         <v>10500</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="2">
+      <c r="H83">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I83" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J83" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
         <v>45921</v>
       </c>
-      <c r="B84" t="s">
-        <v>9</v>
+      <c r="B84" t="str">
+        <f t="shared" si="5"/>
+        <v>domingo</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D84" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -2372,22 +3777,35 @@
       <c r="F84">
         <v>3800</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="7">
         <v>19000</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="2">
+      <c r="H84">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I84" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="J84" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
         <v>45922</v>
       </c>
-      <c r="B85" t="s">
-        <v>13</v>
+      <c r="B85" t="str">
+        <f t="shared" si="5"/>
+        <v>lunes</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -2395,22 +3813,35 @@
       <c r="F85">
         <v>3300</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="7">
         <v>9900</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="2">
+      <c r="H85">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I85" s="2">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="J85" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
         <v>45923</v>
       </c>
-      <c r="B86" t="s">
-        <v>7</v>
+      <c r="B86" t="str">
+        <f t="shared" si="5"/>
+        <v>martes</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -2418,22 +3849,35 @@
       <c r="F86">
         <v>4500</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="7">
         <v>13500</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="2">
+      <c r="H86">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I86" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="J86" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
         <v>45924</v>
       </c>
-      <c r="B87" t="s">
-        <v>11</v>
+      <c r="B87" t="str">
+        <f t="shared" si="5"/>
+        <v>miércoles</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -2441,22 +3885,35 @@
       <c r="F87">
         <v>3800</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="7">
         <v>3800</v>
       </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="2">
+      <c r="H87">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I87" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="J87" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
         <v>45925</v>
       </c>
-      <c r="B88" t="s">
-        <v>8</v>
+      <c r="B88" t="str">
+        <f t="shared" si="5"/>
+        <v>jueves</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E88">
         <v>3</v>
@@ -2464,22 +3921,35 @@
       <c r="F88">
         <v>3300</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="7">
         <v>9900</v>
       </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="2">
+      <c r="H88">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I88" s="2">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="J88" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
         <v>45926</v>
       </c>
-      <c r="B89" t="s">
-        <v>11</v>
+      <c r="B89" t="str">
+        <f t="shared" si="5"/>
+        <v>viernes</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E89">
         <v>3</v>
@@ -2487,22 +3957,35 @@
       <c r="F89">
         <v>3800</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="7">
         <v>11400</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="2">
+      <c r="H89">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I89" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="J89" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>semana</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
         <v>45927</v>
       </c>
-      <c r="B90" t="s">
-        <v>12</v>
+      <c r="B90" t="str">
+        <f t="shared" si="5"/>
+        <v>sábado</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E90">
         <v>4</v>
@@ -2510,22 +3993,35 @@
       <c r="F90">
         <v>4500</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="7">
         <v>18000</v>
       </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" s="2">
+      <c r="H90">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I90" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="J90" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
         <v>45928</v>
       </c>
-      <c r="B91" t="s">
-        <v>11</v>
+      <c r="B91" t="str">
+        <f t="shared" si="5"/>
+        <v>domingo</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -2533,11 +4029,54 @@
       <c r="F91">
         <v>3800</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="7">
         <v>11400</v>
       </c>
+      <c r="H91">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="I91" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="J91" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>finde</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D93">
+        <f>SUBTOTAL(3,D2:D81)</f>
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="G1 G92:G1048576">
+    <cfRule type="expression" dxfId="2" priority="5">
+      <formula>G2=MAX($G$2:$G$91)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G91">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>G2=MAX($G$2:$G$91)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="아메리카노">
+      <formula>NOT(ISERROR(SEARCH("아메리카노",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F704173-6BB6-4E14-9722-19802E306A00}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
+++ b/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data-portfolio\excel-analysis\analysis-cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D374F0FA-2B85-4663-8A44-304FCC86C6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4470350C-40E0-4389-81C8-CB61A4B9A3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="분석" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">데이터!$D$1:$D$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">데이터!$B$1:$B$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="36">
   <si>
     <t>날짜</t>
   </si>
@@ -136,15 +136,45 @@
   <si>
     <t>판매량</t>
   </si>
+  <si>
+    <t>요일별 매출 합</t>
+  </si>
+  <si>
+    <t>lunes</t>
+  </si>
+  <si>
+    <t>martes</t>
+  </si>
+  <si>
+    <t>miércoles</t>
+  </si>
+  <si>
+    <t>jueves</t>
+  </si>
+  <si>
+    <t>viernes</t>
+  </si>
+  <si>
+    <t>sábado</t>
+  </si>
+  <si>
+    <t>domingo</t>
+  </si>
+  <si>
+    <t>최대 매출 요일</t>
+  </si>
+  <si>
+    <t>최소 매출 요일</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +190,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -169,7 +205,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -192,6 +228,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -202,25 +264,20 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -239,139 +296,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -675,19 +599,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -722,7 +646,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="3">
         <v>45839</v>
       </c>
       <c r="B2" t="str">
@@ -741,7 +665,7 @@
       <c r="F2">
         <v>3000</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>15000</v>
       </c>
       <c r="H2">
@@ -752,17 +676,17 @@
         <f>WEEKDAY(A2)</f>
         <v>3</v>
       </c>
-      <c r="J2" s="5" t="str">
+      <c r="J2" s="3" t="str">
         <f>IF((I2=1)+(I2=7),"finde","semana")</f>
         <v>semana</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <f>SUM(G2:G91)</f>
         <v>1038700</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>45840</v>
       </c>
       <c r="B3" t="str">
@@ -781,7 +705,7 @@
       <c r="F3">
         <v>3500</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>17500</v>
       </c>
       <c r="H3">
@@ -792,13 +716,13 @@
         <f t="shared" ref="I3:I66" si="2">WEEKDAY(A3)</f>
         <v>4</v>
       </c>
-      <c r="J3" s="5" t="str">
+      <c r="J3" s="3" t="str">
         <f t="shared" ref="J3:J66" si="3">IF((I3=1)+(I3=7),"finde","semana")</f>
         <v>semana</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>45841</v>
       </c>
       <c r="B4" t="str">
@@ -817,7 +741,7 @@
       <c r="F4">
         <v>3800</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>11400</v>
       </c>
       <c r="H4">
@@ -828,7 +752,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J4" s="5" t="str">
+      <c r="J4" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -837,7 +761,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>45842</v>
       </c>
       <c r="B5" t="str">
@@ -856,7 +780,7 @@
       <c r="F5">
         <v>3500</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>14000</v>
       </c>
       <c r="H5">
@@ -867,17 +791,17 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J5" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
-      </c>
-      <c r="K5" s="6">
+      <c r="J5" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K5" s="4">
         <f>AVERAGE(G2:G91)</f>
         <v>11541.111111111111</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>45843</v>
       </c>
       <c r="B6" t="str">
@@ -896,7 +820,7 @@
       <c r="F6">
         <v>3000</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>15000</v>
       </c>
       <c r="H6">
@@ -907,13 +831,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J6" s="5" t="str">
+      <c r="J6" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>45844</v>
       </c>
       <c r="B7" t="str">
@@ -932,7 +856,7 @@
       <c r="F7">
         <v>3500</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>17500</v>
       </c>
       <c r="H7">
@@ -943,7 +867,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J7" s="5" t="str">
+      <c r="J7" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
@@ -955,7 +879,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>45845</v>
       </c>
       <c r="B8" t="str">
@@ -974,7 +898,7 @@
       <c r="F8">
         <v>3800</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>11400</v>
       </c>
       <c r="H8">
@@ -985,21 +909,21 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J8" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
-      </c>
-      <c r="K8" s="6">
+      <c r="J8" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K8" s="4">
         <f>MAX(G2:G91)</f>
         <v>22500</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <f>MIN(G2:G91)</f>
         <v>3300</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>45846</v>
       </c>
       <c r="B9" t="str">
@@ -1018,7 +942,7 @@
       <c r="F9">
         <v>3500</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>3500</v>
       </c>
       <c r="H9">
@@ -1029,13 +953,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J9" s="5" t="str">
+      <c r="J9" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>45847</v>
       </c>
       <c r="B10" t="str">
@@ -1054,7 +978,7 @@
       <c r="F10">
         <v>3500</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>10500</v>
       </c>
       <c r="H10">
@@ -1065,7 +989,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J10" s="5" t="str">
+      <c r="J10" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -1077,7 +1001,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>45848</v>
       </c>
       <c r="B11" t="str">
@@ -1096,7 +1020,7 @@
       <c r="F11">
         <v>3000</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>6000</v>
       </c>
       <c r="H11">
@@ -1107,7 +1031,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J11" s="5" t="str">
+      <c r="J11" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -1116,12 +1040,12 @@
         <v>아메리카노</v>
       </c>
       <c r="L11">
-        <f>COUNTIF(D2:D91, K11)</f>
-        <v>14</v>
+        <f>SUMIF(D2:D91, K11,E2:E91)</f>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>45849</v>
       </c>
       <c r="B12" t="str">
@@ -1140,7 +1064,7 @@
       <c r="F12">
         <v>3800</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <v>7600</v>
       </c>
       <c r="H12">
@@ -1151,7 +1075,7 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J12" s="5" t="str">
+      <c r="J12" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -1159,12 +1083,12 @@
         <v>라떼</v>
       </c>
       <c r="L12">
-        <f t="shared" ref="L12:L15" si="4">COUNTIF(D3:D92, K12)</f>
-        <v>20</v>
+        <f t="shared" ref="L12:L15" si="4">SUMIF(D3:D92, K12,E3:E92)</f>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13" s="3">
         <v>45850</v>
       </c>
       <c r="B13" t="str">
@@ -1183,7 +1107,7 @@
       <c r="F13">
         <v>3000</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>6000</v>
       </c>
       <c r="H13">
@@ -1194,7 +1118,7 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J13" s="5" t="str">
+      <c r="J13" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
@@ -1203,11 +1127,11 @@
       </c>
       <c r="L13">
         <f t="shared" si="4"/>
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="3">
         <v>45851</v>
       </c>
       <c r="B14" t="str">
@@ -1226,7 +1150,7 @@
       <c r="F14">
         <v>3800</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>19000</v>
       </c>
       <c r="H14">
@@ -1237,7 +1161,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J14" s="5" t="str">
+      <c r="J14" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
@@ -1246,11 +1170,11 @@
       </c>
       <c r="L14">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="3">
         <v>45852</v>
       </c>
       <c r="B15" t="str">
@@ -1269,7 +1193,7 @@
       <c r="F15">
         <v>3800</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>15200</v>
       </c>
       <c r="H15">
@@ -1280,7 +1204,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J15" s="5" t="str">
+      <c r="J15" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -1289,11 +1213,11 @@
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16" s="3">
         <v>45853</v>
       </c>
       <c r="B16" t="str">
@@ -1312,7 +1236,7 @@
       <c r="F16">
         <v>3300</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>3300</v>
       </c>
       <c r="H16">
@@ -1323,13 +1247,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J16" s="5" t="str">
+      <c r="J16" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17" s="3">
         <v>45854</v>
       </c>
       <c r="B17" t="str">
@@ -1348,7 +1272,7 @@
       <c r="F17">
         <v>3300</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>3300</v>
       </c>
       <c r="H17">
@@ -1359,7 +1283,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J17" s="5" t="str">
+      <c r="J17" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
@@ -1371,7 +1295,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>45855</v>
       </c>
       <c r="B18" t="str">
@@ -1390,7 +1314,7 @@
       <c r="F18">
         <v>3500</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <v>10500</v>
       </c>
       <c r="H18">
@@ -1401,21 +1325,21 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J18" s="5" t="str">
+      <c r="J18" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
       <c r="K18" t="str" cm="1">
-        <f t="array" ref="K18">_xlfn.XLOOKUP(MAX(L11:L15), L11:L15,_xlfn.ANCHORARRAY(K11))</f>
+        <f t="array" ref="K18">_xlfn.XLOOKUP(MAX(L11:L15),L11:L15,_xlfn.ANCHORARRAY(K11))</f>
         <v>바닐라라떼</v>
       </c>
       <c r="L18" t="str" cm="1">
-        <f t="array" ref="L18:L19">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(K11),L11:L15 = MIN(L11:L15))</f>
-        <v>아메리카노</v>
+        <f t="array" ref="L18">_xlfn.XLOOKUP(MIN(L11:L15),L11:L15,_xlfn.ANCHORARRAY(K11))</f>
+        <v>카푸치노</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>45856</v>
       </c>
       <c r="B19" t="str">
@@ -1434,7 +1358,7 @@
       <c r="F19">
         <v>3500</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="5">
         <v>7000</v>
       </c>
       <c r="H19">
@@ -1445,16 +1369,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J19" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
-      </c>
-      <c r="L19" t="str">
-        <v>카푸치노</v>
+      <c r="J19" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+      <c r="A20" s="3">
         <v>45857</v>
       </c>
       <c r="B20" t="str">
@@ -1473,7 +1394,7 @@
       <c r="F20">
         <v>3500</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="5">
         <v>14000</v>
       </c>
       <c r="H20">
@@ -1484,13 +1405,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J20" s="5" t="str">
+      <c r="J20" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="3">
         <v>45858</v>
       </c>
       <c r="B21" t="str">
@@ -1509,7 +1430,7 @@
       <c r="F21">
         <v>3500</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="5">
         <v>3500</v>
       </c>
       <c r="H21">
@@ -1520,13 +1441,17 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J21" s="5" t="str">
+      <c r="J21" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
+      <c r="K21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+      <c r="A22" s="3">
         <v>45859</v>
       </c>
       <c r="B22" t="str">
@@ -1545,7 +1470,7 @@
       <c r="F22">
         <v>4500</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="5">
         <v>4500</v>
       </c>
       <c r="H22">
@@ -1556,13 +1481,20 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J22" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J22" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="5" cm="1">
+        <f t="array" ref="L22:L28">SUMIF(B2:B91,K22:K28,G2:G91)</f>
+        <v>141600</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23" s="3">
         <v>45860</v>
       </c>
       <c r="B23" t="str">
@@ -1581,7 +1513,7 @@
       <c r="F23">
         <v>3000</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="5">
         <v>6000</v>
       </c>
       <c r="H23">
@@ -1592,13 +1524,19 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J23" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J23" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="5">
+        <v>147500</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+      <c r="A24" s="3">
         <v>45861</v>
       </c>
       <c r="B24" t="str">
@@ -1617,7 +1555,7 @@
       <c r="F24">
         <v>3500</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="5">
         <v>14000</v>
       </c>
       <c r="H24">
@@ -1628,13 +1566,19 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J24" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J24" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="5">
+        <v>146100</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>45862</v>
       </c>
       <c r="B25" t="str">
@@ -1653,7 +1597,7 @@
       <c r="F25">
         <v>3300</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="5">
         <v>6600</v>
       </c>
       <c r="H25">
@@ -1664,13 +1608,19 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J25" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J25" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K25" t="s">
+        <v>30</v>
+      </c>
+      <c r="L25" s="5">
+        <v>137700</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
+      <c r="A26" s="3">
         <v>45863</v>
       </c>
       <c r="B26" t="str">
@@ -1689,7 +1639,7 @@
       <c r="F26">
         <v>3800</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="5">
         <v>15200</v>
       </c>
       <c r="H26">
@@ -1700,13 +1650,19 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J26" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="5">
+        <v>152600</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
+      <c r="A27" s="3">
         <v>45864</v>
       </c>
       <c r="B27" t="str">
@@ -1725,7 +1681,7 @@
       <c r="F27">
         <v>4500</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="5">
         <v>9000</v>
       </c>
       <c r="H27">
@@ -1736,13 +1692,19 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J27" s="5" t="str">
+      <c r="J27" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="5">
+        <v>142800</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>45865</v>
       </c>
       <c r="B28" t="str">
@@ -1761,7 +1723,7 @@
       <c r="F28">
         <v>4500</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="5">
         <v>22500</v>
       </c>
       <c r="H28">
@@ -1772,13 +1734,19 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J28" s="5" t="str">
+      <c r="J28" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="5">
+        <v>170400</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
+      <c r="A29" s="3">
         <v>45866</v>
       </c>
       <c r="B29" t="str">
@@ -1797,7 +1765,7 @@
       <c r="F29">
         <v>3000</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="5">
         <v>9000</v>
       </c>
       <c r="H29">
@@ -1808,13 +1776,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J29" s="5" t="str">
+      <c r="J29" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="3">
         <v>45867</v>
       </c>
       <c r="B30" t="str">
@@ -1833,7 +1801,7 @@
       <c r="F30">
         <v>3500</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="5">
         <v>10500</v>
       </c>
       <c r="H30">
@@ -1844,13 +1812,20 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J30" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J30" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" t="str" cm="1">
+        <f t="array" ref="L30">_xlfn.XLOOKUP(MAX(_xlfn.ANCHORARRAY(L22)),_xlfn.ANCHORARRAY(L22),K22:K28)</f>
+        <v>domingo</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+      <c r="A31" s="3">
         <v>45868</v>
       </c>
       <c r="B31" t="str">
@@ -1869,7 +1844,7 @@
       <c r="F31">
         <v>3000</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="5">
         <v>9000</v>
       </c>
       <c r="H31">
@@ -1880,13 +1855,20 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J31" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
+      <c r="J31" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>semana</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L31" t="str" cm="1">
+        <f t="array" ref="L31">_xlfn.XLOOKUP(MIN(_xlfn.ANCHORARRAY(L22)),_xlfn.ANCHORARRAY(L22),K22:K28)</f>
+        <v>jueves</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="3">
         <v>45869</v>
       </c>
       <c r="B32" t="str">
@@ -1905,7 +1887,7 @@
       <c r="F32">
         <v>3300</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="5">
         <v>16500</v>
       </c>
       <c r="H32">
@@ -1916,13 +1898,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J32" s="5" t="str">
+      <c r="J32" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="A33" s="3">
         <v>45870</v>
       </c>
       <c r="B33" t="str">
@@ -1941,7 +1923,7 @@
       <c r="F33">
         <v>4500</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="5">
         <v>13500</v>
       </c>
       <c r="H33">
@@ -1952,13 +1934,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J33" s="5" t="str">
+      <c r="J33" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="A34" s="3">
         <v>45871</v>
       </c>
       <c r="B34" t="str">
@@ -1977,7 +1959,7 @@
       <c r="F34">
         <v>3500</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="5">
         <v>14000</v>
       </c>
       <c r="H34">
@@ -1988,13 +1970,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J34" s="5" t="str">
+      <c r="J34" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+      <c r="A35" s="3">
         <v>45872</v>
       </c>
       <c r="B35" t="str">
@@ -2013,7 +1995,7 @@
       <c r="F35">
         <v>4500</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="5">
         <v>13500</v>
       </c>
       <c r="H35">
@@ -2024,13 +2006,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J35" s="5" t="str">
+      <c r="J35" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="A36" s="3">
         <v>45873</v>
       </c>
       <c r="B36" t="str">
@@ -2049,7 +2031,7 @@
       <c r="F36">
         <v>3800</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="5">
         <v>19000</v>
       </c>
       <c r="H36">
@@ -2060,13 +2042,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J36" s="5" t="str">
+      <c r="J36" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+      <c r="A37" s="3">
         <v>45874</v>
       </c>
       <c r="B37" t="str">
@@ -2085,7 +2067,7 @@
       <c r="F37">
         <v>3800</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="5">
         <v>11400</v>
       </c>
       <c r="H37">
@@ -2096,13 +2078,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J37" s="5" t="str">
+      <c r="J37" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+      <c r="A38" s="3">
         <v>45875</v>
       </c>
       <c r="B38" t="str">
@@ -2121,7 +2103,7 @@
       <c r="F38">
         <v>4500</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="5">
         <v>9000</v>
       </c>
       <c r="H38">
@@ -2132,13 +2114,13 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J38" s="5" t="str">
+      <c r="J38" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+      <c r="A39" s="3">
         <v>45876</v>
       </c>
       <c r="B39" t="str">
@@ -2157,7 +2139,7 @@
       <c r="F39">
         <v>3500</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="5">
         <v>17500</v>
       </c>
       <c r="H39">
@@ -2168,13 +2150,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J39" s="5" t="str">
+      <c r="J39" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="A40" s="3">
         <v>45877</v>
       </c>
       <c r="B40" t="str">
@@ -2193,7 +2175,7 @@
       <c r="F40">
         <v>4500</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="5">
         <v>9000</v>
       </c>
       <c r="H40">
@@ -2204,13 +2186,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J40" s="5" t="str">
+      <c r="J40" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+      <c r="A41" s="3">
         <v>45878</v>
       </c>
       <c r="B41" t="str">
@@ -2229,7 +2211,7 @@
       <c r="F41">
         <v>3300</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="5">
         <v>3300</v>
       </c>
       <c r="H41">
@@ -2240,13 +2222,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J41" s="5" t="str">
+      <c r="J41" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
+      <c r="A42" s="3">
         <v>45879</v>
       </c>
       <c r="B42" t="str">
@@ -2265,7 +2247,7 @@
       <c r="F42">
         <v>3300</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="5">
         <v>16500</v>
       </c>
       <c r="H42">
@@ -2276,13 +2258,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J42" s="5" t="str">
+      <c r="J42" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+      <c r="A43" s="3">
         <v>45880</v>
       </c>
       <c r="B43" t="str">
@@ -2301,7 +2283,7 @@
       <c r="F43">
         <v>3800</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="5">
         <v>19000</v>
       </c>
       <c r="H43">
@@ -2312,13 +2294,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J43" s="5" t="str">
+      <c r="J43" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
+      <c r="A44" s="3">
         <v>45881</v>
       </c>
       <c r="B44" t="str">
@@ -2337,7 +2319,7 @@
       <c r="F44">
         <v>3000</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="5">
         <v>15000</v>
       </c>
       <c r="H44">
@@ -2348,13 +2330,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J44" s="5" t="str">
+      <c r="J44" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
+      <c r="A45" s="3">
         <v>45882</v>
       </c>
       <c r="B45" t="str">
@@ -2373,7 +2355,7 @@
       <c r="F45">
         <v>3800</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="5">
         <v>19000</v>
       </c>
       <c r="H45">
@@ -2384,13 +2366,13 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J45" s="5" t="str">
+      <c r="J45" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
+      <c r="A46" s="3">
         <v>45883</v>
       </c>
       <c r="B46" t="str">
@@ -2409,7 +2391,7 @@
       <c r="F46">
         <v>3000</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="5">
         <v>6000</v>
       </c>
       <c r="H46">
@@ -2420,13 +2402,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J46" s="5" t="str">
+      <c r="J46" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47" t="str">
@@ -2445,7 +2427,7 @@
       <c r="F47">
         <v>4500</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="5">
         <v>18000</v>
       </c>
       <c r="H47">
@@ -2456,13 +2438,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J47" s="5" t="str">
+      <c r="J47" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
+      <c r="A48" s="3">
         <v>45885</v>
       </c>
       <c r="B48" t="str">
@@ -2481,7 +2463,7 @@
       <c r="F48">
         <v>3500</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="5">
         <v>14000</v>
       </c>
       <c r="H48">
@@ -2492,13 +2474,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J48" s="5" t="str">
+      <c r="J48" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
+      <c r="A49" s="3">
         <v>45886</v>
       </c>
       <c r="B49" t="str">
@@ -2517,7 +2499,7 @@
       <c r="F49">
         <v>3500</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="5">
         <v>7000</v>
       </c>
       <c r="H49">
@@ -2528,13 +2510,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J49" s="5" t="str">
+      <c r="J49" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
+      <c r="A50" s="3">
         <v>45887</v>
       </c>
       <c r="B50" t="str">
@@ -2553,7 +2535,7 @@
       <c r="F50">
         <v>4500</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="5">
         <v>13500</v>
       </c>
       <c r="H50">
@@ -2564,13 +2546,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J50" s="5" t="str">
+      <c r="J50" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
+      <c r="A51" s="3">
         <v>45888</v>
       </c>
       <c r="B51" t="str">
@@ -2589,7 +2571,7 @@
       <c r="F51">
         <v>3000</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="5">
         <v>9000</v>
       </c>
       <c r="H51">
@@ -2600,13 +2582,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J51" s="5" t="str">
+      <c r="J51" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="5">
+      <c r="A52" s="3">
         <v>45889</v>
       </c>
       <c r="B52" t="str">
@@ -2625,7 +2607,7 @@
       <c r="F52">
         <v>3300</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="5">
         <v>9900</v>
       </c>
       <c r="H52">
@@ -2636,13 +2618,13 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J52" s="5" t="str">
+      <c r="J52" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
+      <c r="A53" s="3">
         <v>45890</v>
       </c>
       <c r="B53" t="str">
@@ -2661,7 +2643,7 @@
       <c r="F53">
         <v>3500</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="5">
         <v>10500</v>
       </c>
       <c r="H53">
@@ -2672,13 +2654,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J53" s="5" t="str">
+      <c r="J53" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="5">
+      <c r="A54" s="3">
         <v>45891</v>
       </c>
       <c r="B54" t="str">
@@ -2697,7 +2679,7 @@
       <c r="F54">
         <v>3500</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="5">
         <v>10500</v>
       </c>
       <c r="H54">
@@ -2708,13 +2690,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J54" s="5" t="str">
+      <c r="J54" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
+      <c r="A55" s="3">
         <v>45892</v>
       </c>
       <c r="B55" t="str">
@@ -2733,7 +2715,7 @@
       <c r="F55">
         <v>3500</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="5">
         <v>10500</v>
       </c>
       <c r="H55">
@@ -2744,13 +2726,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J55" s="5" t="str">
+      <c r="J55" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
+      <c r="A56" s="3">
         <v>45893</v>
       </c>
       <c r="B56" t="str">
@@ -2769,7 +2751,7 @@
       <c r="F56">
         <v>3800</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="5">
         <v>11400</v>
       </c>
       <c r="H56">
@@ -2780,13 +2762,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J56" s="5" t="str">
+      <c r="J56" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+      <c r="A57" s="3">
         <v>45894</v>
       </c>
       <c r="B57" t="str">
@@ -2805,7 +2787,7 @@
       <c r="F57">
         <v>4500</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="5">
         <v>13500</v>
       </c>
       <c r="H57">
@@ -2816,13 +2798,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J57" s="5" t="str">
+      <c r="J57" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="5">
+      <c r="A58" s="3">
         <v>45895</v>
       </c>
       <c r="B58" t="str">
@@ -2841,7 +2823,7 @@
       <c r="F58">
         <v>4500</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="5">
         <v>22500</v>
       </c>
       <c r="H58">
@@ -2852,13 +2834,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J58" s="5" t="str">
+      <c r="J58" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
+      <c r="A59" s="3">
         <v>45896</v>
       </c>
       <c r="B59" t="str">
@@ -2877,7 +2859,7 @@
       <c r="F59">
         <v>3800</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="5">
         <v>7600</v>
       </c>
       <c r="H59">
@@ -2888,13 +2870,13 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J59" s="5" t="str">
+      <c r="J59" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="5">
+      <c r="A60" s="3">
         <v>45897</v>
       </c>
       <c r="B60" t="str">
@@ -2913,7 +2895,7 @@
       <c r="F60">
         <v>3800</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="5">
         <v>3800</v>
       </c>
       <c r="H60">
@@ -2924,13 +2906,13 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="J60" s="5" t="str">
+      <c r="J60" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
+      <c r="A61" s="3">
         <v>45898</v>
       </c>
       <c r="B61" t="str">
@@ -2949,7 +2931,7 @@
       <c r="F61">
         <v>3300</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="5">
         <v>3300</v>
       </c>
       <c r="H61">
@@ -2960,13 +2942,13 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J61" s="5" t="str">
+      <c r="J61" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="5">
+      <c r="A62" s="3">
         <v>45899</v>
       </c>
       <c r="B62" t="str">
@@ -2985,7 +2967,7 @@
       <c r="F62">
         <v>3000</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="5">
         <v>6000</v>
       </c>
       <c r="H62">
@@ -2996,13 +2978,13 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="J62" s="5" t="str">
+      <c r="J62" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="5">
+      <c r="A63" s="3">
         <v>45900</v>
       </c>
       <c r="B63" t="str">
@@ -3021,7 +3003,7 @@
       <c r="F63">
         <v>3300</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="5">
         <v>6600</v>
       </c>
       <c r="H63">
@@ -3032,13 +3014,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J63" s="5" t="str">
+      <c r="J63" s="3" t="str">
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="5">
+      <c r="A64" s="3">
         <v>45901</v>
       </c>
       <c r="B64" t="str">
@@ -3057,7 +3039,7 @@
       <c r="F64">
         <v>3800</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G64" s="5">
         <v>11400</v>
       </c>
       <c r="H64">
@@ -3068,13 +3050,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J64" s="5" t="str">
+      <c r="J64" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
+      <c r="A65" s="3">
         <v>45902</v>
       </c>
       <c r="B65" t="str">
@@ -3093,7 +3075,7 @@
       <c r="F65">
         <v>4500</v>
       </c>
-      <c r="G65" s="7">
+      <c r="G65" s="5">
         <v>18000</v>
       </c>
       <c r="H65">
@@ -3104,13 +3086,13 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J65" s="5" t="str">
+      <c r="J65" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
+      <c r="A66" s="3">
         <v>45903</v>
       </c>
       <c r="B66" t="str">
@@ -3129,7 +3111,7 @@
       <c r="F66">
         <v>4500</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="5">
         <v>22500</v>
       </c>
       <c r="H66">
@@ -3140,13 +3122,13 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J66" s="5" t="str">
+      <c r="J66" s="3" t="str">
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
+      <c r="A67" s="3">
         <v>45904</v>
       </c>
       <c r="B67" t="str">
@@ -3165,7 +3147,7 @@
       <c r="F67">
         <v>4500</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="5">
         <v>18000</v>
       </c>
       <c r="H67">
@@ -3176,13 +3158,13 @@
         <f t="shared" ref="I67:I91" si="7">WEEKDAY(A67)</f>
         <v>5</v>
       </c>
-      <c r="J67" s="5" t="str">
+      <c r="J67" s="3" t="str">
         <f t="shared" ref="J67:J91" si="8">IF((I67=1)+(I67=7),"finde","semana")</f>
         <v>semana</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
+      <c r="A68" s="3">
         <v>45905</v>
       </c>
       <c r="B68" t="str">
@@ -3201,7 +3183,7 @@
       <c r="F68">
         <v>3800</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="5">
         <v>7600</v>
       </c>
       <c r="H68">
@@ -3212,13 +3194,13 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="J68" s="5" t="str">
+      <c r="J68" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
+      <c r="A69" s="3">
         <v>45906</v>
       </c>
       <c r="B69" t="str">
@@ -3237,7 +3219,7 @@
       <c r="F69">
         <v>4500</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G69" s="5">
         <v>18000</v>
       </c>
       <c r="H69">
@@ -3248,13 +3230,13 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="J69" s="5" t="str">
+      <c r="J69" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
+      <c r="A70" s="3">
         <v>45907</v>
       </c>
       <c r="B70" t="str">
@@ -3273,7 +3255,7 @@
       <c r="F70">
         <v>3000</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="5">
         <v>9000</v>
       </c>
       <c r="H70">
@@ -3284,13 +3266,13 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J70" s="5" t="str">
+      <c r="J70" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="5">
+      <c r="A71" s="3">
         <v>45908</v>
       </c>
       <c r="B71" t="str">
@@ -3309,7 +3291,7 @@
       <c r="F71">
         <v>3800</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="5">
         <v>11400</v>
       </c>
       <c r="H71">
@@ -3320,13 +3302,13 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="J71" s="5" t="str">
+      <c r="J71" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
+      <c r="A72" s="3">
         <v>45909</v>
       </c>
       <c r="B72" t="str">
@@ -3345,7 +3327,7 @@
       <c r="F72">
         <v>3300</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G72" s="5">
         <v>13200</v>
       </c>
       <c r="H72">
@@ -3356,13 +3338,13 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="J72" s="5" t="str">
+      <c r="J72" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
+      <c r="A73" s="3">
         <v>45910</v>
       </c>
       <c r="B73" t="str">
@@ -3381,7 +3363,7 @@
       <c r="F73">
         <v>3500</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="5">
         <v>14000</v>
       </c>
       <c r="H73">
@@ -3392,13 +3374,13 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="J73" s="5" t="str">
+      <c r="J73" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
+      <c r="A74" s="3">
         <v>45911</v>
       </c>
       <c r="B74" t="str">
@@ -3417,7 +3399,7 @@
       <c r="F74">
         <v>4500</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G74" s="5">
         <v>9000</v>
       </c>
       <c r="H74">
@@ -3428,13 +3410,13 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="J74" s="5" t="str">
+      <c r="J74" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="5">
+      <c r="A75" s="3">
         <v>45912</v>
       </c>
       <c r="B75" t="str">
@@ -3453,7 +3435,7 @@
       <c r="F75">
         <v>3800</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="5">
         <v>19000</v>
       </c>
       <c r="H75">
@@ -3464,13 +3446,13 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="J75" s="5" t="str">
+      <c r="J75" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
+      <c r="A76" s="3">
         <v>45913</v>
       </c>
       <c r="B76" t="str">
@@ -3489,7 +3471,7 @@
       <c r="F76">
         <v>4500</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="5">
         <v>4500</v>
       </c>
       <c r="H76">
@@ -3500,13 +3482,13 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="J76" s="5" t="str">
+      <c r="J76" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
+      <c r="A77" s="3">
         <v>45914</v>
       </c>
       <c r="B77" t="str">
@@ -3525,7 +3507,7 @@
       <c r="F77">
         <v>4500</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="5">
         <v>13500</v>
       </c>
       <c r="H77">
@@ -3536,13 +3518,13 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J77" s="5" t="str">
+      <c r="J77" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
+      <c r="A78" s="3">
         <v>45915</v>
       </c>
       <c r="B78" t="str">
@@ -3561,7 +3543,7 @@
       <c r="F78">
         <v>3800</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G78" s="5">
         <v>3800</v>
       </c>
       <c r="H78">
@@ -3572,13 +3554,13 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="J78" s="5" t="str">
+      <c r="J78" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
+      <c r="A79" s="3">
         <v>45916</v>
       </c>
       <c r="B79" t="str">
@@ -3597,7 +3579,7 @@
       <c r="F79">
         <v>3300</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G79" s="5">
         <v>6600</v>
       </c>
       <c r="H79">
@@ -3608,13 +3590,13 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="J79" s="5" t="str">
+      <c r="J79" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
+      <c r="A80" s="3">
         <v>45917</v>
       </c>
       <c r="B80" t="str">
@@ -3633,7 +3615,7 @@
       <c r="F80">
         <v>3000</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G80" s="5">
         <v>6000</v>
       </c>
       <c r="H80">
@@ -3644,13 +3626,13 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="J80" s="5" t="str">
+      <c r="J80" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
+      <c r="A81" s="3">
         <v>45918</v>
       </c>
       <c r="B81" t="str">
@@ -3669,7 +3651,7 @@
       <c r="F81">
         <v>3000</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="5">
         <v>12000</v>
       </c>
       <c r="H81">
@@ -3680,13 +3662,13 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="J81" s="5" t="str">
+      <c r="J81" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
+      <c r="A82" s="3">
         <v>45919</v>
       </c>
       <c r="B82" t="str">
@@ -3705,7 +3687,7 @@
       <c r="F82">
         <v>3300</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="5">
         <v>16500</v>
       </c>
       <c r="H82">
@@ -3716,13 +3698,13 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="J82" s="5" t="str">
+      <c r="J82" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
+      <c r="A83" s="3">
         <v>45920</v>
       </c>
       <c r="B83" t="str">
@@ -3741,7 +3723,7 @@
       <c r="F83">
         <v>3500</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="5">
         <v>10500</v>
       </c>
       <c r="H83">
@@ -3752,13 +3734,13 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="J83" s="5" t="str">
+      <c r="J83" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
+      <c r="A84" s="3">
         <v>45921</v>
       </c>
       <c r="B84" t="str">
@@ -3777,7 +3759,7 @@
       <c r="F84">
         <v>3800</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="5">
         <v>19000</v>
       </c>
       <c r="H84">
@@ -3788,13 +3770,13 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J84" s="5" t="str">
+      <c r="J84" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
+      <c r="A85" s="3">
         <v>45922</v>
       </c>
       <c r="B85" t="str">
@@ -3813,7 +3795,7 @@
       <c r="F85">
         <v>3300</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G85" s="5">
         <v>9900</v>
       </c>
       <c r="H85">
@@ -3824,13 +3806,13 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="J85" s="5" t="str">
+      <c r="J85" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="5">
+      <c r="A86" s="3">
         <v>45923</v>
       </c>
       <c r="B86" t="str">
@@ -3849,7 +3831,7 @@
       <c r="F86">
         <v>4500</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="5">
         <v>13500</v>
       </c>
       <c r="H86">
@@ -3860,13 +3842,13 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="J86" s="5" t="str">
+      <c r="J86" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
+      <c r="A87" s="3">
         <v>45924</v>
       </c>
       <c r="B87" t="str">
@@ -3885,7 +3867,7 @@
       <c r="F87">
         <v>3800</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="5">
         <v>3800</v>
       </c>
       <c r="H87">
@@ -3896,13 +3878,13 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="J87" s="5" t="str">
+      <c r="J87" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
+      <c r="A88" s="3">
         <v>45925</v>
       </c>
       <c r="B88" t="str">
@@ -3921,7 +3903,7 @@
       <c r="F88">
         <v>3300</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="5">
         <v>9900</v>
       </c>
       <c r="H88">
@@ -3932,13 +3914,13 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="J88" s="5" t="str">
+      <c r="J88" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
+      <c r="A89" s="3">
         <v>45926</v>
       </c>
       <c r="B89" t="str">
@@ -3957,7 +3939,7 @@
       <c r="F89">
         <v>3800</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G89" s="5">
         <v>11400</v>
       </c>
       <c r="H89">
@@ -3968,13 +3950,13 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="J89" s="5" t="str">
+      <c r="J89" s="3" t="str">
         <f t="shared" si="8"/>
         <v>semana</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
+      <c r="A90" s="3">
         <v>45927</v>
       </c>
       <c r="B90" t="str">
@@ -3993,7 +3975,7 @@
       <c r="F90">
         <v>4500</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="5">
         <v>18000</v>
       </c>
       <c r="H90">
@@ -4004,13 +3986,13 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="J90" s="5" t="str">
+      <c r="J90" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
+      <c r="A91" s="3">
         <v>45928</v>
       </c>
       <c r="B91" t="str">
@@ -4029,7 +4011,7 @@
       <c r="F91">
         <v>3800</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="5">
         <v>11400</v>
       </c>
       <c r="H91">
@@ -4040,32 +4022,33 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J91" s="5" t="str">
+      <c r="J91" s="3" t="str">
         <f t="shared" si="8"/>
         <v>finde</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D93">
-        <f>SUBTOTAL(3,D2:D81)</f>
-        <v>80</v>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E92">
+        <f>SUBTOTAL(9, E2:E81)</f>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:B93" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="아메리카노">
+      <formula>NOT(ISERROR(SEARCH("아메리카노",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G1 G92:G1048576">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>G2=MAX($G$2:$G$91)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G91">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>G2=MAX($G$2:$G$91)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="아메리카노">
-      <formula>NOT(ISERROR(SEARCH("아메리카노",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
+++ b/excel-analysis/analysis-cafe/카페_매출_데이터_샘플_작업본.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data-portfolio\excel-analysis\analysis-cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4470350C-40E0-4389-81C8-CB61A4B9A3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD87F0A3-EA7D-4CD5-9AEF-3EB67DFF940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="37">
   <si>
     <t>날짜</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>최소 매출 요일</t>
+  </si>
+  <si>
+    <t>요일별 매출 평균</t>
   </si>
 </sst>
 </file>
@@ -599,14 +602,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1666,7 +1669,7 @@
         <v>45864</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A27, "dddd")</f>
         <v>sábado</v>
       </c>
       <c r="C27" t="s">
@@ -1903,7 +1906,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>45870</v>
       </c>
@@ -1939,7 +1942,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>45871</v>
       </c>
@@ -1974,8 +1977,12 @@
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>45872</v>
       </c>
@@ -2010,8 +2017,19 @@
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="5">
+        <f>AVERAGEIF(B:B,K35,G:G)</f>
+        <v>11800</v>
+      </c>
+      <c r="M35">
+        <f>_xlfn.RANK.EQ(L35,$L$35:$L$41)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>45873</v>
       </c>
@@ -2046,8 +2064,19 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="5">
+        <f t="shared" ref="L36:L41" si="5">AVERAGEIF(B:B,K36,G:G)</f>
+        <v>11346.153846153846</v>
+      </c>
+      <c r="M36">
+        <f t="shared" ref="M36:M41" si="6">_xlfn.RANK.EQ(L36,$L$35:$L$41)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45874</v>
       </c>
@@ -2082,8 +2111,19 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>29</v>
+      </c>
+      <c r="L37" s="5">
+        <f t="shared" si="5"/>
+        <v>11238.461538461539</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45875</v>
       </c>
@@ -2118,8 +2158,19 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="5">
+        <f t="shared" si="5"/>
+        <v>10592.307692307691</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>45876</v>
       </c>
@@ -2154,8 +2205,19 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="5">
+        <f t="shared" si="5"/>
+        <v>11738.461538461539</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>45877</v>
       </c>
@@ -2190,8 +2252,19 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="5">
+        <f t="shared" si="5"/>
+        <v>10984.615384615385</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>45878</v>
       </c>
@@ -2226,8 +2299,19 @@
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" s="5">
+        <f t="shared" si="5"/>
+        <v>13107.692307692309</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>45879</v>
       </c>
@@ -2263,7 +2347,7 @@
         <v>finde</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>45880</v>
       </c>
@@ -2298,8 +2382,15 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="5" t="str" cm="1">
+        <f t="array" ref="K43:L49">_xlfn._xlws.SORT(K35:L41,2,-1)</f>
+        <v>domingo</v>
+      </c>
+      <c r="L43" s="5">
+        <v>13107.692307692309</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>45881</v>
       </c>
@@ -2334,8 +2425,14 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" t="str">
+        <v>lunes</v>
+      </c>
+      <c r="L44" s="5">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>45882</v>
       </c>
@@ -2370,8 +2467,14 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" t="str">
+        <v>viernes</v>
+      </c>
+      <c r="L45" s="5">
+        <v>11738.461538461539</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45883</v>
       </c>
@@ -2406,8 +2509,14 @@
         <f t="shared" si="3"/>
         <v>semana</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" t="str">
+        <v>martes</v>
+      </c>
+      <c r="L46" s="5">
+        <v>11346.153846153846</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45884</v>
       </c>
@@ -2438,12 +2547,17 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="J47" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>semana</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K47" t="str">
+        <v>miércoles</v>
+      </c>
+      <c r="L47" s="5">
+        <v>11238.461538461539</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>45885</v>
       </c>
@@ -2478,8 +2592,14 @@
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" t="str">
+        <v>sábado</v>
+      </c>
+      <c r="L48" s="5">
+        <v>10984.615384615385</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45886</v>
       </c>
@@ -2514,8 +2634,14 @@
         <f t="shared" si="3"/>
         <v>finde</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" t="str">
+        <v>jueves</v>
+      </c>
+      <c r="L49" s="5">
+        <v>10592.307692307691</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>45887</v>
       </c>
@@ -2551,7 +2677,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>45888</v>
       </c>
@@ -2587,7 +2713,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>45889</v>
       </c>
@@ -2623,7 +2749,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>45890</v>
       </c>
@@ -2659,7 +2785,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>45891</v>
       </c>
@@ -2695,7 +2821,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>45892</v>
       </c>
@@ -2731,7 +2857,7 @@
         <v>finde</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>45893</v>
       </c>
@@ -2767,7 +2893,7 @@
         <v>finde</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>45894</v>
       </c>
@@ -2803,7 +2929,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>45895</v>
       </c>
@@ -2839,7 +2965,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>45896</v>
       </c>
@@ -2875,7 +3001,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>45897</v>
       </c>
@@ -2911,7 +3037,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>45898</v>
       </c>
@@ -2947,7 +3073,7 @@
         <v>semana</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>45899</v>
       </c>
@@ -2983,7 +3109,7 @@
         <v>finde</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>45900</v>
       </c>
@@ -3019,7 +3145,7 @@
         <v>finde</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>45901</v>
       </c>
@@ -3132,7 +3258,7 @@
         <v>45904</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B91" si="5">TEXT(A67, "dddd")</f>
+        <f t="shared" ref="B67:B91" si="7">TEXT(A67, "dddd")</f>
         <v>jueves</v>
       </c>
       <c r="C67" t="s">
@@ -3151,15 +3277,15 @@
         <v>18000</v>
       </c>
       <c r="H67">
-        <f t="shared" ref="H67:H91" si="6">MONTH(A67)</f>
+        <f t="shared" ref="H67:H91" si="8">MONTH(A67)</f>
         <v>9</v>
       </c>
       <c r="I67" s="2">
-        <f t="shared" ref="I67:I91" si="7">WEEKDAY(A67)</f>
+        <f t="shared" ref="I67:I91" si="9">WEEKDAY(A67)</f>
         <v>5</v>
       </c>
       <c r="J67" s="3" t="str">
-        <f t="shared" ref="J67:J91" si="8">IF((I67=1)+(I67=7),"finde","semana")</f>
+        <f t="shared" ref="J67:J91" si="10">IF((I67=1)+(I67=7),"finde","semana")</f>
         <v>semana</v>
       </c>
     </row>
@@ -3168,7 +3294,7 @@
         <v>45905</v>
       </c>
       <c r="B68" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>viernes</v>
       </c>
       <c r="C68" t="s">
@@ -3187,15 +3313,15 @@
         <v>7600</v>
       </c>
       <c r="H68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I68" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="J68" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3204,7 +3330,7 @@
         <v>45906</v>
       </c>
       <c r="B69" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>sábado</v>
       </c>
       <c r="C69" t="s">
@@ -3223,15 +3349,15 @@
         <v>18000</v>
       </c>
       <c r="H69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I69" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="J69" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3240,7 +3366,7 @@
         <v>45907</v>
       </c>
       <c r="B70" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>domingo</v>
       </c>
       <c r="C70" t="s">
@@ -3259,15 +3385,15 @@
         <v>9000</v>
       </c>
       <c r="H70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I70" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J70" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3276,7 +3402,7 @@
         <v>45908</v>
       </c>
       <c r="B71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>lunes</v>
       </c>
       <c r="C71" t="s">
@@ -3295,15 +3421,15 @@
         <v>11400</v>
       </c>
       <c r="H71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I71" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="J71" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3312,7 +3438,7 @@
         <v>45909</v>
       </c>
       <c r="B72" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>martes</v>
       </c>
       <c r="C72" t="s">
@@ -3331,15 +3457,15 @@
         <v>13200</v>
       </c>
       <c r="H72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I72" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="J72" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3348,7 +3474,7 @@
         <v>45910</v>
       </c>
       <c r="B73" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>miércoles</v>
       </c>
       <c r="C73" t="s">
@@ -3367,15 +3493,15 @@
         <v>14000</v>
       </c>
       <c r="H73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J73" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3384,7 +3510,7 @@
         <v>45911</v>
       </c>
       <c r="B74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>jueves</v>
       </c>
       <c r="C74" t="s">
@@ -3403,15 +3529,15 @@
         <v>9000</v>
       </c>
       <c r="H74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I74" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="J74" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3420,7 +3546,7 @@
         <v>45912</v>
       </c>
       <c r="B75" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>viernes</v>
       </c>
       <c r="C75" t="s">
@@ -3439,15 +3565,15 @@
         <v>19000</v>
       </c>
       <c r="H75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I75" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="J75" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3456,7 +3582,7 @@
         <v>45913</v>
       </c>
       <c r="B76" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>sábado</v>
       </c>
       <c r="C76" t="s">
@@ -3475,15 +3601,15 @@
         <v>4500</v>
       </c>
       <c r="H76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I76" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="J76" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3492,7 +3618,7 @@
         <v>45914</v>
       </c>
       <c r="B77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>domingo</v>
       </c>
       <c r="C77" t="s">
@@ -3511,15 +3637,15 @@
         <v>13500</v>
       </c>
       <c r="H77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I77" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J77" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3528,7 +3654,7 @@
         <v>45915</v>
       </c>
       <c r="B78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>lunes</v>
       </c>
       <c r="C78" t="s">
@@ -3547,15 +3673,15 @@
         <v>3800</v>
       </c>
       <c r="H78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I78" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="J78" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3564,7 +3690,7 @@
         <v>45916</v>
       </c>
       <c r="B79" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>martes</v>
       </c>
       <c r="C79" t="s">
@@ -3583,15 +3709,15 @@
         <v>6600</v>
       </c>
       <c r="H79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I79" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="J79" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3600,7 +3726,7 @@
         <v>45917</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>miércoles</v>
       </c>
       <c r="C80" t="s">
@@ -3619,15 +3745,15 @@
         <v>6000</v>
       </c>
       <c r="H80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J80" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3636,7 +3762,7 @@
         <v>45918</v>
       </c>
       <c r="B81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>jueves</v>
       </c>
       <c r="C81" t="s">
@@ -3655,15 +3781,15 @@
         <v>12000</v>
       </c>
       <c r="H81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I81" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="J81" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3672,7 +3798,7 @@
         <v>45919</v>
       </c>
       <c r="B82" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>viernes</v>
       </c>
       <c r="C82" t="s">
@@ -3691,15 +3817,15 @@
         <v>16500</v>
       </c>
       <c r="H82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I82" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="J82" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3708,7 +3834,7 @@
         <v>45920</v>
       </c>
       <c r="B83" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>sábado</v>
       </c>
       <c r="C83" t="s">
@@ -3727,15 +3853,15 @@
         <v>10500</v>
       </c>
       <c r="H83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="J83" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3744,7 +3870,7 @@
         <v>45921</v>
       </c>
       <c r="B84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>domingo</v>
       </c>
       <c r="C84" t="s">
@@ -3763,15 +3889,15 @@
         <v>19000</v>
       </c>
       <c r="H84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I84" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J84" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3780,7 +3906,7 @@
         <v>45922</v>
       </c>
       <c r="B85" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>lunes</v>
       </c>
       <c r="C85" t="s">
@@ -3799,15 +3925,15 @@
         <v>9900</v>
       </c>
       <c r="H85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I85" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="J85" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3816,7 +3942,7 @@
         <v>45923</v>
       </c>
       <c r="B86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>martes</v>
       </c>
       <c r="C86" t="s">
@@ -3835,15 +3961,15 @@
         <v>13500</v>
       </c>
       <c r="H86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I86" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="J86" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3852,7 +3978,7 @@
         <v>45924</v>
       </c>
       <c r="B87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>miércoles</v>
       </c>
       <c r="C87" t="s">
@@ -3871,15 +3997,15 @@
         <v>3800</v>
       </c>
       <c r="H87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I87" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J87" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3888,7 +4014,7 @@
         <v>45925</v>
       </c>
       <c r="B88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>jueves</v>
       </c>
       <c r="C88" t="s">
@@ -3907,15 +4033,15 @@
         <v>9900</v>
       </c>
       <c r="H88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I88" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="J88" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3924,7 +4050,7 @@
         <v>45926</v>
       </c>
       <c r="B89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>viernes</v>
       </c>
       <c r="C89" t="s">
@@ -3943,15 +4069,15 @@
         <v>11400</v>
       </c>
       <c r="H89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="J89" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>semana</v>
       </c>
     </row>
@@ -3960,7 +4086,7 @@
         <v>45927</v>
       </c>
       <c r="B90" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>sábado</v>
       </c>
       <c r="C90" t="s">
@@ -3979,15 +4105,15 @@
         <v>18000</v>
       </c>
       <c r="H90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I90" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="J90" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
@@ -3996,7 +4122,7 @@
         <v>45928</v>
       </c>
       <c r="B91" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>domingo</v>
       </c>
       <c r="C91" t="s">
@@ -4015,23 +4141,36 @@
         <v>11400</v>
       </c>
       <c r="H91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J91" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>finde</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D92">
+        <f>COUNTIF(D2:D81,"아메리카노")</f>
+        <v>14</v>
+      </c>
       <c r="E92">
         <f>SUBTOTAL(9, E2:E81)</f>
         <v>248</v>
       </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D93">
+        <f>SUBTOTAL(3,D2:D91)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G94" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:B93" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
